--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>93.37590492904214</v>
+        <v>15.17358455096935</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7333543768024353</v>
+        <v>0.1191700862303957</v>
       </c>
       <c r="E2" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F2" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>102.6759539484574</v>
+        <v>16.68484251662433</v>
       </c>
       <c r="D3" t="n">
-        <v>14.85038138097784</v>
+        <v>2.413186974408899</v>
       </c>
       <c r="E3" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F3" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.64440874635824</v>
+        <v>5.304716421283214</v>
       </c>
       <c r="D4" t="n">
-        <v>32.02420990135898</v>
+        <v>5.203934108970834</v>
       </c>
       <c r="E4" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F4" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.63711695270806</v>
+        <v>4.328531504815059</v>
       </c>
       <c r="D5" t="n">
-        <v>26.09367097098298</v>
+        <v>4.240221532784734</v>
       </c>
       <c r="E5" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F5" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>90.72229389072314</v>
+        <v>14.74237275724251</v>
       </c>
       <c r="D6" t="n">
-        <v>18.23571982853277</v>
+        <v>2.963304472136576</v>
       </c>
       <c r="E6" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F6" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.39141276413862</v>
+        <v>3.638604574172526</v>
       </c>
       <c r="D7" t="n">
-        <v>21.68930093643312</v>
+        <v>3.524511402170382</v>
       </c>
       <c r="E7" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F7" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.34614386509323</v>
+        <v>5.74374837807765</v>
       </c>
       <c r="D8" t="n">
-        <v>22.13999865619715</v>
+        <v>3.597749781632036</v>
       </c>
       <c r="E8" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F8" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.85089514656051</v>
+        <v>3.225770461316083</v>
       </c>
       <c r="D9" t="n">
-        <v>19.36226041577061</v>
+        <v>3.146367317562724</v>
       </c>
       <c r="E9" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F9" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>5.441974240085637</v>
+        <v>0.884320814013916</v>
       </c>
       <c r="D10" t="n">
-        <v>4.539459055269835</v>
+        <v>0.7376620964813482</v>
       </c>
       <c r="E10" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F10" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.63678277720061</v>
+        <v>8.553477201295099</v>
       </c>
       <c r="D11" t="n">
-        <v>11.18033988749895</v>
+        <v>1.816805231718579</v>
       </c>
       <c r="E11" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F11" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>52.87319791422795</v>
+        <v>8.591894661062042</v>
       </c>
       <c r="D12" t="n">
-        <v>15.08776565565135</v>
+        <v>2.451761919043344</v>
       </c>
       <c r="E12" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F12" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.75692572479814</v>
+        <v>7.760500430279698</v>
       </c>
       <c r="D13" t="n">
-        <v>11.09547223565683</v>
+        <v>1.803014238294234</v>
       </c>
       <c r="E13" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F13" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.85573770782396</v>
+        <v>6.151557377521393</v>
       </c>
       <c r="D14" t="n">
-        <v>8.517688746334333</v>
+        <v>1.384124421279329</v>
       </c>
       <c r="E14" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F14" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.1866276879029</v>
+        <v>5.067826999284221</v>
       </c>
       <c r="D15" t="n">
-        <v>17.99359954830853</v>
+        <v>2.923959926600136</v>
       </c>
       <c r="E15" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F15" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.52649535119892</v>
+        <v>5.285555494569826</v>
       </c>
       <c r="D16" t="n">
-        <v>17.00484219106625</v>
+        <v>2.763286856048266</v>
       </c>
       <c r="E16" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F16" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.22318496986238</v>
+        <v>4.748767557602637</v>
       </c>
       <c r="D17" t="n">
-        <v>13.03781310460234</v>
+        <v>2.118644629497881</v>
       </c>
       <c r="E17" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F17" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39.54092754531003</v>
+        <v>6.425400726112881</v>
       </c>
       <c r="D18" t="n">
-        <v>38.76701106192526</v>
+        <v>6.299639297562855</v>
       </c>
       <c r="E18" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F18" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.30660475702452</v>
+        <v>7.037323273016486</v>
       </c>
       <c r="D19" t="n">
-        <v>24.10444306220848</v>
+        <v>3.916971997608878</v>
       </c>
       <c r="E19" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F19" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>34.29416996054011</v>
+        <v>5.572802618587768</v>
       </c>
       <c r="D20" t="n">
-        <v>34.1622541840139</v>
+        <v>5.551366304902259</v>
       </c>
       <c r="E20" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F20" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>30.02009591046771</v>
+        <v>4.878265585451004</v>
       </c>
       <c r="D21" t="n">
-        <v>31.48097455605865</v>
+        <v>5.11565836535953</v>
       </c>
       <c r="E21" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F21" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>9.304716320601573</v>
+        <v>1.512016402097756</v>
       </c>
       <c r="D22" t="n">
-        <v>15.37947815831757</v>
+        <v>2.499165200726606</v>
       </c>
       <c r="E22" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F22" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>38.05646253731513</v>
+        <v>6.18417516231371</v>
       </c>
       <c r="D23" t="n">
-        <v>31.76449023298261</v>
+        <v>5.161729662859675</v>
       </c>
       <c r="E23" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F23" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>21.33976005281518</v>
+        <v>3.467711008582468</v>
       </c>
       <c r="D24" t="n">
-        <v>23.06137845785713</v>
+        <v>3.747473999401783</v>
       </c>
       <c r="E24" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F24" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>17.48666124708556</v>
+        <v>2.841582452651403</v>
       </c>
       <c r="D25" t="n">
-        <v>18.51083471705659</v>
+        <v>3.008010641521696</v>
       </c>
       <c r="E25" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F25" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>28.07638369823158</v>
+        <v>4.562412350962632</v>
       </c>
       <c r="D26" t="n">
-        <v>27.40323506896162</v>
+        <v>4.453025698706264</v>
       </c>
       <c r="E26" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F26" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>13.73440511740728</v>
+        <v>2.231840831578683</v>
       </c>
       <c r="D27" t="n">
-        <v>12.81914515049803</v>
+        <v>2.083111086955929</v>
       </c>
       <c r="E27" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F27" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>8.130242340159231</v>
+        <v>1.321164380275875</v>
       </c>
       <c r="D28" t="n">
-        <v>6.476531291312416</v>
+        <v>1.052436334838268</v>
       </c>
       <c r="E28" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F28" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>16.5521199048367</v>
+        <v>2.689719484535964</v>
       </c>
       <c r="D29" t="n">
-        <v>14.77089587263663</v>
+        <v>2.400270579303453</v>
       </c>
       <c r="E29" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F29" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>37.12151851035917</v>
+        <v>6.032246757933365</v>
       </c>
       <c r="D30" t="n">
-        <v>31.86843514723298</v>
+        <v>5.178620711425359</v>
       </c>
       <c r="E30" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F30" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>26.31094209825513</v>
+        <v>4.275528090966459</v>
       </c>
       <c r="D31" t="n">
-        <v>24.62046468413232</v>
+        <v>4.000825511171501</v>
       </c>
       <c r="E31" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F31" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>23.79300612734376</v>
+        <v>3.866363495693361</v>
       </c>
       <c r="D32" t="n">
-        <v>22.0406660715365</v>
+        <v>3.581608236624681</v>
       </c>
       <c r="E32" t="n">
-        <v>22.94760607208701</v>
+        <v>3.728985986714139</v>
       </c>
       <c r="F32" t="n">
-        <v>9.081993329296473</v>
+        <v>1.475823916010677</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
